--- a/tools/importer/reports/import-adventure-listing.report.xlsx
+++ b/tools/importer/reports/import-adventure-listing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-28T13:15:10.457Z</t>
+    <t>2026-08-28T14:25:03.334Z</t>
   </si>
   <si>
     <t>WKND Adventures and Travel</t>
@@ -73,7 +73,7 @@
     <t>adventure-listing</t>
   </si>
   <si>
-    <t>2026-08-28T13:59:28.631Z</t>
+    <t>2026-08-28T14:25:08.767Z</t>
   </si>
   <si>
     <t>Adventures</t>
@@ -82,6 +82,48 @@
     <t>https://wknd.site/us/en/adventures.html</t>
   </si>
   <si>
+    <t>us/en/faqs.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-faq"]</t>
+  </si>
+  <si>
+    <t>us/en/faqs</t>
+  </si>
+  <si>
+    <t>faq-page</t>
+  </si>
+  <si>
+    <t>2026-08-28T13:59:49.194Z</t>
+  </si>
+  <si>
+    <t>FAQs</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/faqs.html</t>
+  </si>
+  <si>
+    <t>us/en/magazine.report.json</t>
+  </si>
+  <si>
+    <t>["columns","cards"]</t>
+  </si>
+  <si>
+    <t>us/en/magazine</t>
+  </si>
+  <si>
+    <t>content-listing</t>
+  </si>
+  <si>
+    <t>2026-08-28T13:59:42.282Z</t>
+  </si>
+  <si>
+    <t>Magazine</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/magazine.html</t>
+  </si>
+  <si>
     <t>us/en/adventures/bali-surf-camp.report.json</t>
   </si>
   <si>
@@ -101,6 +143,27 @@
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/bali-surf-camp.html</t>
+  </si>
+  <si>
+    <t>us/en/magazine/arctic-surfing.report.json</t>
+  </si>
+  <si>
+    <t>["cards"]</t>
+  </si>
+  <si>
+    <t>us/en/magazine/arctic-surfing</t>
+  </si>
+  <si>
+    <t>article-detail</t>
+  </si>
+  <si>
+    <t>2026-08-28T14:24:39.064Z</t>
+  </si>
+  <si>
+    <t>Arctic Surfing</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/magazine/arctic-surfing.html</t>
   </si>
 </sst>
 </file>
@@ -489,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
@@ -605,6 +668,84 @@
         <v>29</v>
       </c>
     </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
